--- a/data/trans_bre/IP16A98-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Provincia-trans_bre.xlsx
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-39,1; -1,33</t>
+          <t>-38,49; -0,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 35,38</t>
+          <t>-8,62; 32,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 47,06</t>
+          <t>-11,95; 52,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,19 +654,19 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,27; 1124,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-66,07; 761,57</t>
+          <t>-61,04; 1008,8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -714,39 +714,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 14,89</t>
+          <t>-13,55; 15,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 15,39</t>
+          <t>-12,71; 16,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 16,44</t>
+          <t>-15,04; 15,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 479,57</t>
+          <t>-82,76; 455,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-84,67; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,2; 243,59</t>
+          <t>-84,65; 238,13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -794,22 +794,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 28,09</t>
+          <t>-8,41; 27,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,58; 38,12</t>
+          <t>-33,81; 31,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-32,84; 12,86</t>
+          <t>-33,93; 11,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-76,5; —</t>
+          <t>-67,15; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,98; 112,57</t>
+          <t>-86,08; 87,78</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,43; 4,76</t>
+          <t>-34,75; 4,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,36; 17,74</t>
+          <t>-25,88; 16,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 35,45</t>
+          <t>-26,6; 34,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 212,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,51; 96,03</t>
+          <t>-61,81; 80,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,64; —</t>
+          <t>-92,93; —</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 10,03</t>
+          <t>-18,55; 9,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-51,24; 24,24</t>
+          <t>-52,38; 22,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-44,51; 19,4</t>
+          <t>-46,16; 19,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 41,62</t>
+          <t>-8,55; 41,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,54; 2,66</t>
+          <t>-61,65; 6,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,89; 8,19</t>
+          <t>-34,88; 8,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 95,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 401,77</t>
+          <t>-100,0; 412,54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1114,22 +1114,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-23,36; 5,5</t>
+          <t>-23,61; 5,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 22,53</t>
+          <t>-13,33; 25,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 11,29</t>
+          <t>-32,23; 10,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 115,6</t>
+          <t>-100,0; 96,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-84,78; 106,92</t>
+          <t>-85,47; 90,79</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 16,92</t>
+          <t>-25,82; 16,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 6,04</t>
+          <t>-29,67; 6,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 54,35</t>
+          <t>-17,12; 53,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-73,95; 144,28</t>
+          <t>-72,56; 120,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,55; 59,22</t>
+          <t>-88,19; 63,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,34; 841,6</t>
+          <t>-58,22; 807,96</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 3,51</t>
+          <t>-9,76; 3,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 4,18</t>
+          <t>-11,55; 3,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 9,54</t>
+          <t>-10,16; 10,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 31,75</t>
+          <t>-52,47; 30,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 26,03</t>
+          <t>-45,9; 24,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-49,2; 64,24</t>
+          <t>-45,17; 72,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A98-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Provincia-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-38,49; -0,88</t>
+          <t>-38,19; -1,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 32,26</t>
+          <t>-6,44; 35,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 52,77</t>
+          <t>-12,64; 48,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-65,7; 943,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-61,04; 1008,8</t>
+          <t>-61,72; 754,52</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 15,09</t>
+          <t>-12,92; 15,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 16,53</t>
+          <t>-12,63; 17,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 15,96</t>
+          <t>-13,51; 15,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-82,76; 455,33</t>
+          <t>-80,49; 401,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-84,67; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,65; 238,13</t>
+          <t>-80,66; 230,64</t>
         </is>
       </c>
     </row>
@@ -794,22 +794,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 27,99</t>
+          <t>-10,28; 28,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 31,61</t>
+          <t>-26,47; 37,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 11,72</t>
+          <t>-30,65; 11,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-67,15; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-86,08; 87,78</t>
+          <t>-84,17; 101,69</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 4,11</t>
+          <t>-34,92; 5,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,88; 16,41</t>
+          <t>-24,39; 19,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 34,13</t>
+          <t>-24,17; 38,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 212,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,81; 80,12</t>
+          <t>-57,22; 100,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,93; —</t>
+          <t>-89,39; —</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,55; 9,76</t>
+          <t>-18,49; 9,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 22,98</t>
+          <t>-49,27; 24,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-46,16; 19,88</t>
+          <t>-45,08; 23,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 385,14</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 41,22</t>
+          <t>-9,1; 42,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-61,65; 6,07</t>
+          <t>-63,47; 5,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,88; 8,12</t>
+          <t>-35,77; 6,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,39; 1019,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 75,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 412,54</t>
+          <t>-100,0; 466,54</t>
         </is>
       </c>
     </row>
@@ -1114,22 +1114,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 5,12</t>
+          <t>-22,22; 6,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 25,21</t>
+          <t>-13,43; 24,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-32,23; 10,14</t>
+          <t>-29,07; 11,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 96,45</t>
+          <t>-90,79; 169,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-85,47; 90,79</t>
+          <t>-84,79; 133,36</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 16,89</t>
+          <t>-28,16; 16,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 6,47</t>
+          <t>-28,36; 5,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 53,36</t>
+          <t>-15,08; 53,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-72,56; 120,66</t>
+          <t>-73,41; 119,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,19; 63,17</t>
+          <t>-88,54; 57,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-58,22; 807,96</t>
+          <t>-69,23; 683,79</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 3,44</t>
+          <t>-9,87; 3,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 3,97</t>
+          <t>-11,43; 4,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 10,82</t>
+          <t>-11,78; 9,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-52,47; 30,8</t>
+          <t>-51,33; 29,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 24,54</t>
+          <t>-45,24; 32,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-45,17; 72,56</t>
+          <t>-49,8; 63,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A98-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Provincia-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que consumieron otros medicamentos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,83</t>
+          <t>-1,87</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>-10,05%</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-38,19; -1,1</t>
+          <t>-39,1; -1,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 35,27</t>
+          <t>-7,28; 35,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 48,29</t>
+          <t>-19,47; 16,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-65,7; 943,52</t>
+          <t>-73,27; 1124,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-61,72; 754,52</t>
+          <t>-72,28; 197,69</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,44</t>
+          <t>10,32</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>113,43%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 15,53</t>
+          <t>-13,92; 14,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 17,97</t>
+          <t>-12,61; 15,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 15,58</t>
+          <t>-2,61; 23,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-80,49; 401,14</t>
+          <t>-100,0; 479,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,66; 230,64</t>
+          <t>-30,11; 510,41</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-9,11</t>
+          <t>-7,32</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-34,11%</t>
+          <t>-30,94%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 28,2</t>
+          <t>-10,55; 28,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 37,13</t>
+          <t>-26,58; 38,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-30,65; 11,92</t>
+          <t>-29,37; 13,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>-76,5; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-84,17; 101,69</t>
+          <t>-82,75; 129,48</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,38</t>
+          <t>10,41</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>63,88%</t>
         </is>
       </c>
     </row>
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 5,75</t>
+          <t>-31,43; 4,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 19,03</t>
+          <t>-23,36; 17,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 38,71</t>
+          <t>-22,07; 38,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,22; 100,47</t>
+          <t>-60,51; 96,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-89,39; —</t>
+          <t>-80,27; —</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-7,11</t>
+          <t>-9,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-26,82%</t>
+          <t>-30,32%</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 9,65</t>
+          <t>-17,86; 10,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-49,27; 24,36</t>
+          <t>-51,24; 24,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-45,08; 23,04</t>
+          <t>-49,86; 19,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 385,14</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-13,45</t>
+          <t>-12,22</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-66,95%</t>
+          <t>-61,68%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 42,54</t>
+          <t>-8,7; 41,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,47; 5,4</t>
+          <t>-64,54; 2,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,77; 6,99</t>
+          <t>-35,79; 11,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-90,39; 1019,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,31</t>
+          <t>-100,0; 95,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 466,54</t>
+          <t>-100,0; 538,77</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-6,01</t>
+          <t>-5,99</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-27,44%</t>
+          <t>-27,21%</t>
         </is>
       </c>
     </row>
@@ -1114,22 +1114,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-22,22; 6,6</t>
+          <t>-23,36; 5,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 24,95</t>
+          <t>-14,55; 22,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 11,75</t>
+          <t>-31,61; 11,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-90,79; 169,38</t>
+          <t>-100,0; 115,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-84,79; 133,36</t>
+          <t>-87,86; 114,47</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>24,81</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>100,74%</t>
+          <t>114,77%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 16,36</t>
+          <t>-27,67; 16,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 5,88</t>
+          <t>-28,45; 6,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 53,6</t>
+          <t>-13,88; 57,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-73,41; 119,67</t>
+          <t>-73,95; 144,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,54; 57,95</t>
+          <t>-88,55; 59,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,23; 683,79</t>
+          <t>-56,47; 935,65</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 3,15</t>
+          <t>-9,31; 3,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 4,8</t>
+          <t>-12,21; 4,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 9,51</t>
+          <t>-8,81; 8,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 29,91</t>
+          <t>-50,93; 31,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 32,38</t>
+          <t>-49,56; 26,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-49,8; 63,97</t>
+          <t>-37,61; 58,71</t>
         </is>
       </c>
     </row>
